--- a/csv/policies/reference/Ref_incandescent phase out/formula_Ref_incandescent phase out_SK.xlsx
+++ b/csv/policies/reference/Ref_incandescent phase out/formula_Ref_incandescent phase out_SK.xlsx
@@ -1,122 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\xCIMS\cims-models\csv\policies\reference\Ref_incandescent phase out\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D318DFB1-301D-4889-87F9-551A04D5682F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="39375" yWindow="4845" windowWidth="17280" windowHeight="8880" xr2:uid="{5492F0E3-1A76-452F-9F5A-A9F6BFCE6F50}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39375" yWindow="4845" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcOnSave="0"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
-  <si>
-    <t>&lt;-- Navigate by typing to search</t>
-  </si>
-  <si>
-    <t>Branch</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>Service</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Context</t>
-  </si>
-  <si>
-    <t>Sub_Context</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>CIMS.CAN.SK.Residential.Dwellings.Lighting</t>
-  </si>
-  <si>
-    <t>SK</t>
-  </si>
-  <si>
-    <t>Residential</t>
-  </si>
-  <si>
-    <t>Lighting</t>
-  </si>
-  <si>
-    <t>Incandescent</t>
-  </si>
-  <si>
-    <t>Market share new_max</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -135,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -469,146 +439,194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53667280-7E20-4498-84C9-89B582A2C1D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:X3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>&lt;-- Navigate by typing to search</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sub_Context</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2030</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2035</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2040</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2045</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2050</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Residential.Dwellings.Lighting</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Incandescent</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Market share new_max</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2">
-        <v>2000</v>
-      </c>
-      <c r="N2">
-        <v>2005</v>
-      </c>
-      <c r="O2">
-        <v>2010</v>
-      </c>
-      <c r="P2">
-        <v>2015</v>
-      </c>
-      <c r="Q2">
-        <v>2020</v>
-      </c>
-      <c r="R2">
-        <v>2025</v>
-      </c>
-      <c r="S2">
-        <v>2030</v>
-      </c>
-      <c r="T2">
-        <v>2035</v>
-      </c>
-      <c r="U2">
-        <v>2040</v>
-      </c>
-      <c r="V2">
-        <v>2045</v>
-      </c>
-      <c r="W2">
-        <v>2050</v>
-      </c>
-      <c r="X2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3">
+      <c r="N3" t="n">
         <v>1</v>
       </c>
-      <c r="N3">
+      <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q3">
-        <v>1E-4</v>
-      </c>
-      <c r="R3">
-        <v>1E-4</v>
-      </c>
-      <c r="S3">
-        <v>1E-4</v>
-      </c>
-      <c r="T3">
-        <v>1E-4</v>
-      </c>
-      <c r="U3">
-        <v>1E-4</v>
-      </c>
-      <c r="V3">
-        <v>1E-4</v>
-      </c>
-      <c r="W3">
-        <v>1E-4</v>
+      <c r="Q3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.0001</v>
       </c>
     </row>
   </sheetData>

--- a/csv/policies/reference/Ref_incandescent phase out/formula_Ref_incandescent phase out_SK.xlsx
+++ b/csv/policies/reference/Ref_incandescent phase out/formula_Ref_incandescent phase out_SK.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39375" yWindow="4845" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -587,7 +587,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
